--- a/template/Bank_KQKD_ReportNormId.v2.xlsx
+++ b/template/Bank_KQKD_ReportNormId.v2.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>ReportNormId</t>
   </si>
@@ -100,6 +100,9 @@
   </si>
   <si>
     <t>TỔNG THU NHẬP HOẠT ĐỘNG</t>
+  </si>
+  <si>
+    <t>Tổng chi phí thuế thu nhập doanh nghiệp</t>
   </si>
 </sst>
 </file>
@@ -710,7 +713,7 @@
         <v>4382</v>
       </c>
       <c r="C22" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15" x14ac:dyDescent="0.2">
